--- a/presentations/heatmap_byhand/xlsx/baseline_methods/cvss_v3/mcp_sqlite_risk_rankings_cvss_v3.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/cvss_v3/mcp_sqlite_risk_rankings_cvss_v3.xlsx
@@ -1767,12 +1767,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1791,6 +1792,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1806,6 +1812,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:L I:N (table-name reconnaissance, limited disclosure) → Medium (5.3)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1821,6 +1832,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:L I:N (schema column-name disclosure) → Medium (5.3)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1836,6 +1852,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:H I:N (SELECT on critical tables: PII, credentials, financial) → Medium (6.5)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1851,6 +1872,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:C C:H I:H A:L (api_keys table: credential theft + lateral movement) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1866,6 +1892,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:C C:N I:L A:L (schema change visible to all DB consumers) → Medium (6.5)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
@@ -1879,6 +1910,11 @@
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:N I:L (append-only note, data-poisoning risk) → Medium (4.3)</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1930,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1918,6 +1955,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1933,6 +1975,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PII tier=critical: read_query C:H → Medium (6.5); write_query I:H A:L → High; write on api_keys S:C → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1948,6 +1995,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Financial tier=critical: read_query C:H → Medium; write_query I:H → High; api_keys path → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1963,6 +2015,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Credentials tier=critical + api_keys table S:C on write_query: C:H I:H A:L → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1978,6 +2035,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tier=high: read_query C:H → Medium (6.5); write_query I:H → High; api_keys write dominates → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -1993,6 +2055,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tier=low; write_query on api_keys S:C C:H I:H still applies → Critical worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2008,6 +2075,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tier=medium/high; worst-case write on api_keys S:C → Critical regardless of data cat row</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2021,6 +2093,11 @@
       <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tier=low; api_keys write_query S:C dominates → Critical worst-case across all rows</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2112,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2059,6 +2137,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -2074,6 +2157,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PII table tier=critical: write_query S:U I:H A:L → High (7.1); read_query C:H → Medium</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -2089,6 +2177,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Metadata tier=medium: write_query I:L A:L → Medium; read_query C:L → Medium</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2104,6 +2197,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mixed tier=medium: write_query I:L → Medium; read_query C:L → Medium</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -2119,6 +2217,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Research tier=high: write_query I:H A:L → High; read_query C:H → Medium</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2134,6 +2237,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Public tier=low: write_query I:N→L → Medium; read_query C:N → Low/Medium</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -2149,6 +2257,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Financial tier=high: write_query I:H A:L → High; read_query C:H → Medium (6.5)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2162,6 +2275,11 @@
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>write_query: S:C C:H I:H A:L (credential modification enables lateral movement) → Critical</t>
         </is>
       </c>
     </row>
